--- a/260603 New data set (reproducibility)/Overpotential DATA raw alt/Air BP/KB BM/30K/KB BM 1.5bp air_edited.xlsx
+++ b/260603 New data set (reproducibility)/Overpotential DATA raw alt/Air BP/KB BM/30K/KB BM 1.5bp air_edited.xlsx
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.5309233673476148</v>
+        <v>-0.492</v>
       </c>
       <c r="V4" s="0" t="n">
         <v>-6</v>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.05753919140479981</v>
+        <v>-0.05195</v>
       </c>
       <c r="V5" s="0" t="n">
         <v>-5.9</v>
